--- a/branches/feature/multi-language/CodeSystem-selftest-palette.xlsx
+++ b/branches/feature/multi-language/CodeSystem-selftest-palette.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T18:36:13+00:00</t>
+    <t>2026-07-22T18:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
